--- a/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
@@ -426,38 +426,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>型号 / 规格</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>封装</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>立创料号（参考）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>规格要求</t>
         </is>
@@ -466,36 +472,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>电容</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>100nF 0402 X7R</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>电容</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>100pF 0402 C0G</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>必须 C0G/NP0，不要 X7R</t>
         </is>
@@ -504,136 +520,170 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1k 0402</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>1uF 0402 X7R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1uF 0402 X7R</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+          <t>YAGEO AC0402CRNPO9BN3R6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>100</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C5552081</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APV AHW1005C-33NJTF</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+          <t>三环 TCC0402COG120J500AT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>100</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>C6807986</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C696888</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DDY WI0402IFR10KST-HF</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+          <t>三环 TCC0402COG3R0C500AT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>100</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>C18221115</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C696883</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>C2830293</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>低结电容 ESD 管（≤0.6pF）</t>
+          <t>风华 0402CG2R7C500NT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C1561</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>YAGEO AC0402CRNPO9BN3R6</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+          <t>风华 0402CG6R2C500NT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>100</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>C5552081</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C41744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>必须 C0G/NP0，不要 X7R</t>
         </is>
@@ -642,621 +692,772 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YAGEO RC0402FR-0752R3L ±1%</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>C273696</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+          <t>100nF 0603 X7R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>muRata LQW15AN27NG0ZD</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>C7519921</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+          <t>100pF 0603 C0G</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>muRata LQW15AN6N8G00D</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>C82919</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
+          <t>12pF 0603 C0G</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>muRata LQW15AN7N5G00D</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>C82918</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
+          <t>15pF 0603 C0G</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>必须 C0G/NP0，不要 X7R</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>三环 TCC0402COG120J500AT</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>C696888</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>1nF 0603 X7R</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>三环 TCC0402COG3R0C500AT</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>C696883</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>1uF 0603 X7R</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>风华 0402CG2R7C500NT</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>C1561</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>200pF 0603 C0G</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>风华 0402CG6R2C500NT</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>C41744</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>3pF 0603 C0G</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0R 0603</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Samsung CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C19666</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100k 0603</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>10uF 0805 X7R</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100nF 0603 X7R</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>22uF 0805 X7R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100pF 0603 C0G</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>1k 0402</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10k 0603</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>YAGEO RC0402FR-0752R3L ±1%</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>C273696</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12pF 0603 C0G</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>50</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>0R 0603</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15pF 0603 C0G</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>50</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+          <t>100k 0603</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>18k 0603</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>50</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>10k 0603</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1k 0603</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>50</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>18k 0603</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1nF 0603 X7R</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>50</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>1k 0603</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1uF 0603 X7R</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>50</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>27R 0603</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>200pF 0603 C0G</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>50</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>4.7k 0603</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27R 0603</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>50</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>5.1k 0603</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3pF 0603 C0G</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>APV AHW1005C-33NJTF</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>C6807986</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4.7k 0603</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>50</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>DDY WI0402IFR10KST-HF</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>C18221115</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5.1k 0603</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>50</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>muRata LQW15AN27NG0ZD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>C7519921</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Samsung CL10A475KO8NNNC</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>50</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>C19666</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>muRata LQW15AN6N8G00D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>C82919</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10uF 0805 X7R</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>50</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>muRata LQW15AN7N5G00D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>C82918</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22uF 0805 X7R</t>
+          <t>二极管</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>50</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>C2830293</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>低结电容 ESD 管（≤0.6pF）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>金瑞 JK-SMD0805-020-30V</t>
+          <t>二极管</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>6</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>C516070</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>JSMSEMI 1N5819W</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOD-123</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>C963381</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JSMSEMI 1N5819W</t>
+          <t>保险丝</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SOD-123</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>C963381</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+          <t>金瑞 JK-SMD0805-020-30V</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>C516070</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>三极管/MOS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>UMW AO3401A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>6</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>C347476</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>信路达 XA17-G4K</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>SOT-363/SC-70-6</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>C513494</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100pF 0402 C0G</t>
+          <t>100pF 0402 X7R</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -511,11 +511,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -525,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1uF 0402 X7R</t>
+          <t>1uF 0402 X5R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -565,7 +561,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+          <t>C0G/NP0，容差 ±0.10pF</t>
         </is>
       </c>
     </row>
@@ -595,7 +591,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+          <t>C0G/NP0，容差 ±5%</t>
         </is>
       </c>
     </row>
@@ -625,7 +621,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+          <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
       </c>
     </row>
@@ -655,7 +651,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+          <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
       </c>
     </row>
@@ -685,7 +681,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+          <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100pF 0603 C0G</t>
+          <t>100pF 0603</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1nF 0603 X7R</t>
+          <t>1nF 0603</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -815,7 +811,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1uF 0603 X7R</t>
+          <t>1uF 0603 X5R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -837,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200pF 0603 C0G</t>
+          <t>200pF 0603</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -859,7 +855,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3pF 0603 C0G</t>
+          <t>3pF 0603</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -907,7 +903,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10uF 0805 X7R</t>
+          <t>10uF 0805 X5R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -929,7 +925,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22uF 0805 X7R</t>
+          <t>22uF 0805 X5R</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -993,11 +989,7 @@
           <t>C273696</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+      <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100nF 0402 X7R</t>
+          <t>100nF 50V 0402 X7R</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100pF 0402 X7R</t>
+          <t>100pF 50V 0402 X7R</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1uF 0402 X5R</t>
+          <t>1uF 16V 0402 X5R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100nF 0603 X7R</t>
+          <t>100nF 50V 0603 X7R</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100pF 0603</t>
+          <t>100pF 50V 0603</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12pF 0603 C0G</t>
+          <t>12pF 50V 0603 C0G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15pF 0603 C0G</t>
+          <t>15pF 50V 0603 C0G</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1nF 0603</t>
+          <t>1nF 50V 0603</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1uF 0603 X5R</t>
+          <t>1uF 25V 0603 X5R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200pF 0603</t>
+          <t>200pF 50V 0603</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3pF 0603</t>
+          <t>3pF 50V 0603</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10uF 0805 X5R</t>
+          <t>10uF 25V 0805 X5R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22uF 0805 X5R</t>
+          <t>22uF 16V 0805 X5R</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">

--- a/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3.1/BOM_采购清单.xlsx
@@ -426,15 +426,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +458,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>材质</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>耐压</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>参考品牌/料号（非强制）</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>立创料号（参考）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>规格要求</t>
         </is>
@@ -477,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100nF 50V 0402 X7R</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,11 +503,22 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>X7R</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -499,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100pF 50V 0402 X7R</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,11 +536,22 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>X7R</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -521,7 +561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1uF 16V 0402 X5R</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,11 +569,34 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>100</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>三环 TCC0402COG120J500AT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>C696888</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>C0G/NP0，容差 ±5%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YAGEO AC0402CRNPO9BN3R6</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,19 +614,22 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16V</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>100</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C5552081</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>C0G/NP0，容差 ±0.10pF</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -573,7 +639,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>三环 TCC0402COG120J500AT</t>
+          <t>2.7pF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,17 +647,32 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C696888</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>C0G/NP0，容差 ±5%</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>风华 0402CG2R7C500NT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>C1561</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
       </c>
     </row>
@@ -603,7 +684,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>三环 TCC0402COG3R0C500AT</t>
+          <t>3.6pF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -611,17 +692,32 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>100</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>C696883</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>C0G/NP0，容差 ±0.25pF</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>YAGEO AC0402CRNPO9BN3R6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C5552081</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>C0G/NP0，容差 ±0.10pF</t>
         </is>
       </c>
     </row>
@@ -633,7 +729,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>风华 0402CG2R7C500NT</t>
+          <t>3pF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -641,15 +737,30 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>C1561</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>三环 TCC0402COG3R0C500AT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C696883</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
@@ -663,23 +774,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>6.2pF</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>风华 0402CG6R2C500NT</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>C41744</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>C0G/NP0，容差 ±0.25pF</t>
         </is>
@@ -693,7 +819,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100nF 50V 0603 X7R</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -701,11 +827,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>X7R</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>50</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -715,7 +852,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100pF 50V 0603</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -723,11 +860,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -737,7 +885,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12pF 50V 0603 C0G</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -745,13 +893,24 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>50</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>建议 C0G（X7R 可用，需实测频偏）</t>
         </is>
       </c>
     </row>
@@ -763,7 +922,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15pF 50V 0603 C0G</t>
+          <t>15pF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -771,13 +930,24 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>50</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>必须 C0G/NP0，不要 X7R</t>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>建议 C0G（X7R 可用，需实测频偏）</t>
         </is>
       </c>
     </row>
@@ -789,7 +959,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1nF 50V 0603</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,11 +967,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>50</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -811,7 +992,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1uF 25V 0603 X5R</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -819,11 +1000,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25V</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>50</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -833,7 +1025,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200pF 50V 0603</t>
+          <t>200pF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -841,11 +1033,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>50</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -855,7 +1058,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3pF 50V 0603</t>
+          <t>3pF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -863,11 +1066,22 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>50</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -877,23 +1091,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>4.7uF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16V</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Samsung CL10A475KO8NNNC</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>C19666</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -903,7 +1132,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10uF 25V 0805 X5R</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -911,11 +1140,22 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>25V</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>50</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -925,7 +1165,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22uF 16V 0805 X5R</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -933,11 +1173,22 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16V</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>50</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -947,7 +1198,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1k 0402</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -955,11 +1206,14 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
         <v>100</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>精度 ±1%</t>
         </is>
@@ -973,23 +1227,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>52.3R</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>YAGEO RC0402FR-0752R3L ±1%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>C273696</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -999,7 +1264,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0R 0603</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1007,11 +1272,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
         <v>50</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1021,7 +1289,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100k 0603</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1029,11 +1297,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
         <v>50</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1043,7 +1314,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10k 0603</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1051,11 +1322,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
         <v>50</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1065,7 +1339,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18k 0603</t>
+          <t>18k</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1073,11 +1347,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
         <v>50</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1087,7 +1364,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1k 0603</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1095,11 +1372,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
         <v>50</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1109,7 +1389,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27R 0603</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1117,11 +1397,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
         <v>50</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1131,7 +1414,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4.7k 0603</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1139,11 +1422,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
         <v>50</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1153,7 +1439,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.1k 0603</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1161,11 +1447,14 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
         <v>50</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1175,7 +1464,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>APV AHW1005C-33NJTF</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1183,15 +1472,26 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
         <v>100</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>C6807986</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DDY WI0402IFR10KST-HF</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>C18221115</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>必须绕线电感，叠层款不行</t>
         </is>
@@ -1205,7 +1505,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DDY WI0402IFR10KST-HF</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1213,15 +1513,26 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
         <v>100</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>C18221115</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>muRata LQW15AN27NG0ZD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>C7519921</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>必须绕线电感，叠层款不行</t>
         </is>
@@ -1235,7 +1546,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>muRata LQW15AN27NG0ZD</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1243,15 +1554,26 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
         <v>100</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>C7519921</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>APV AHW1005C-33NJTF</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>C6807986</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>必须绕线电感，叠层款不行</t>
         </is>
@@ -1265,23 +1587,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>6.8nH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>muRata LQW15AN6N8G00D</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>100</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>C82919</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>必须绕线电感，叠层款不行</t>
         </is>
@@ -1295,23 +1628,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>7.5nH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>muRata LQW15AN7N5G00D</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>100</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>C82918</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>必须绕线电感，叠层款不行</t>
         </is>
@@ -1325,23 +1669,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>ESD 3.3V/0.6pF</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>TECH PUBLIC TPESD8L3.3CT5G</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>C2830293</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>低结电容 ESD 管（≤0.6pF）</t>
         </is>
@@ -1355,23 +1706,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>B5819W</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOD-123</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>JSMSEMI 1N5819W</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SOD-123</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>C963381</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1381,23 +1739,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>金瑞 JK-SMD0805-020-30V</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>C516070</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1407,23 +1772,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>UMW AO3401A</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>C347476</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1433,23 +1805,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOT-363/SC-70-6</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>信路达 XA17-G4K</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SOT-363/SC-70-6</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>C513494</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
